--- a/Assets/Data/Excel/Moon.xlsx
+++ b/Assets/Data/Excel/Moon.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -30,6 +30,24 @@
   </si>
   <si>
     <t>range</t>
+  </si>
+  <si>
+    <t>string（字符串）</t>
+  </si>
+  <si>
+    <t>BuildingType（枚举）</t>
+  </si>
+  <si>
+    <t>Vector2Int</t>
+  </si>
+  <si>
+    <t>int（整数）</t>
+  </si>
+  <si>
+    <t>float（浮点数）</t>
+  </si>
+  <si>
+    <t>基础信息</t>
   </si>
   <si>
     <t/>
@@ -61,13 +79,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -92,9 +115,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -105,7 +129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -129,48 +153,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0">
-        <v>60</v>
-      </c>
-      <c r="F2" s="0">
-        <v>5</v>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0">
-        <v>60</v>
-      </c>
-      <c r="F3" s="0">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>12</v>
@@ -179,12 +203,52 @@
         <v>13</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" s="0">
         <v>60</v>
       </c>
       <c r="F4" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="0">
+        <v>60</v>
+      </c>
+      <c r="F5" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="0">
+        <v>60</v>
+      </c>
+      <c r="F6" s="0">
         <v>5</v>
       </c>
     </row>
